--- a/output/pdf_financials_xlsx/JG.xlsx
+++ b/output/pdf_financials_xlsx/JG.xlsx
@@ -1057,34 +1057,34 @@
         <v>-0.20878</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.736725</v>
+        <v>-3.736725</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.458943</v>
+        <v>-3.458943</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4.392793</v>
+        <v>-4.392793</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.713672</v>
+        <v>-3.713672</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.326795</v>
+        <v>-3.326795</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3.942414</v>
+        <v>-3.942414</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>3.271587</v>
+        <v>-3.271587</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4.156605</v>
+        <v>-4.156605</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>4.985884</v>
+        <v>-4.985884</v>
       </c>
     </row>
     <row r="17">
@@ -1277,34 +1277,34 @@
         <v>-0.20878</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.736725</v>
+        <v>-3.736725</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.458943</v>
+        <v>-3.458943</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4.392793</v>
+        <v>-4.392793</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.713672</v>
+        <v>-3.713672</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.326795</v>
+        <v>-3.326795</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.942414</v>
+        <v>-3.942414</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3.271587</v>
+        <v>-3.271587</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>4.156605</v>
+        <v>-4.156605</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>4.985884</v>
+        <v>-4.985884</v>
       </c>
     </row>
     <row r="21">
@@ -1406,34 +1406,34 @@
         <v>-0.20878</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.736725</v>
+        <v>-3.736725</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.458943</v>
+        <v>-3.458943</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4.392793</v>
+        <v>-4.392793</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.713672</v>
+        <v>-3.713672</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>3.326795</v>
+        <v>-3.326795</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.942414</v>
+        <v>-3.942414</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.271587</v>
+        <v>-3.271587</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>4.156605</v>
+        <v>-4.156605</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>4.985884</v>
+        <v>-4.985884</v>
       </c>
     </row>
     <row r="24">
@@ -1537,25 +1537,25 @@
         <v>10.439</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.500674</v>
+        <v>0.500674</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-62.27875</v>
+        <v>62.27875</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-69.17886</v>
+        <v>69.17886</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-109.819825</v>
+        <v>109.819825</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-185.6836</v>
+        <v>185.6836</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-166.33975</v>
+        <v>166.33975</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-197.1207</v>
+        <v>197.1207</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-207.83025</v>
+        <v>207.83025</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-249.2942</v>
+        <v>249.2942</v>
       </c>
     </row>
     <row r="27">
@@ -1582,34 +1582,34 @@
         <v>-0.208842</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.736725</v>
+        <v>-3.736725</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.458943</v>
+        <v>-3.458943</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.392793</v>
+        <v>-4.392793</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.713672</v>
+        <v>-3.713672</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.326795</v>
+        <v>-3.326795</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>3.942414</v>
+        <v>-3.942414</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3.271587</v>
+        <v>-3.271587</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>4.156605</v>
+        <v>-4.156605</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>4.985884</v>
+        <v>-4.985884</v>
       </c>
     </row>
     <row r="28">
@@ -1668,34 +1668,34 @@
         <v>-0.208842</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.76855</v>
+        <v>-3.7049</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.461319</v>
+        <v>-3.456567</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4.395159</v>
+        <v>-4.390427</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.717344</v>
+        <v>-3.71</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.333234</v>
+        <v>-3.320356</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.947736</v>
+        <v>-3.937092</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3.275721</v>
+        <v>-3.267453</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>4.161498</v>
+        <v>-4.151712</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>4.996113</v>
+        <v>-4.975655</v>
       </c>
     </row>
     <row r="30">
@@ -1778,34 +1778,34 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4744,7 +4744,7 @@
         <v>-0.20878</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-3.736725</v>
@@ -5573,22 +5573,22 @@
         <v>-6.640609</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-4.166462</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-4.500043</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-7.031514</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-2.261072</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.102627</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-2.296747</v>
       </c>
     </row>
     <row r="119">
@@ -13946,7 +13946,11 @@
           <t>Exploration and evaluation expenditures (Note 4)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -15664,7 +15668,11 @@
           <t>Exploration and evaluation expenditure (Note 4)</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -25901,31 +25909,31 @@
         </is>
       </c>
       <c r="H263" s="5" t="n">
-        <v>3.736725</v>
+        <v>-3.736725</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>3.458943</v>
+        <v>-3.458943</v>
       </c>
       <c r="J263" s="5" t="n">
-        <v>4.392793</v>
+        <v>-4.392793</v>
       </c>
       <c r="K263" s="5" t="n">
-        <v>3.713672</v>
+        <v>-3.713672</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>3.326795</v>
+        <v>-3.326795</v>
       </c>
       <c r="M263" s="5" t="n">
-        <v>3.942414</v>
+        <v>-3.942414</v>
       </c>
       <c r="N263" s="5" t="n">
-        <v>3.271587</v>
+        <v>-3.271587</v>
       </c>
       <c r="O263" s="5" t="n">
-        <v>4.156605</v>
+        <v>-4.156605</v>
       </c>
       <c r="P263" s="5" t="n">
-        <v>4.985884</v>
+        <v>-4.985884</v>
       </c>
     </row>
     <row r="264">
@@ -26038,28 +26046,28 @@
         </is>
       </c>
       <c r="I265" s="5" t="n">
-        <v>3.051167</v>
+        <v>-3.051167</v>
       </c>
       <c r="J265" s="5" t="n">
-        <v>4.719728</v>
+        <v>-4.719728</v>
       </c>
       <c r="K265" s="5" t="n">
-        <v>3.379111</v>
+        <v>-3.379111</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>5.044971</v>
+        <v>-5.044971</v>
       </c>
       <c r="M265" s="5" t="n">
-        <v>4.808386</v>
+        <v>-4.808386</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>5.361175</v>
+        <v>-5.361175</v>
       </c>
       <c r="O265" s="5" t="n">
-        <v>4.561029</v>
+        <v>-4.561029</v>
       </c>
       <c r="P265" s="5" t="n">
-        <v>6.246414</v>
+        <v>-6.246414</v>
       </c>
     </row>
     <row r="266">
@@ -29231,10 +29239,10 @@
         </is>
       </c>
       <c r="H309" s="5" t="n">
-        <v>3.833076</v>
+        <v>-3.833076</v>
       </c>
       <c r="I309" s="5" t="n">
-        <v>3.051167</v>
+        <v>-3.051167</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -30916,10 +30924,10 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="H331" s="5" t="n">
-        <v>8.178163</v>
+        <v>-8.178163</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -31070,10 +31078,10 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="H333" s="5" t="n">
-        <v>8.180491</v>
+        <v>-8.180491</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -32738,7 +32746,7 @@
         </is>
       </c>
       <c r="G354" s="5" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
@@ -32896,7 +32904,7 @@
         </is>
       </c>
       <c r="G356" s="5" t="n">
-        <v>0.465627</v>
+        <v>-0.465627</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/JG.xlsx
+++ b/output/pdf_financials_xlsx/JG.xlsx
@@ -888,31 +888,31 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02511</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.029302</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.059915</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.027229</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012533</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.046478</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.092636</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.074478</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.044981</v>
       </c>
     </row>
     <row r="13">
@@ -1585,31 +1585,31 @@
         <v>-0.465627</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.736725</v>
+        <v>-3.711615</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.458943</v>
+        <v>-3.429641</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.392793</v>
+        <v>-4.332878</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.713672</v>
+        <v>-3.686443</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.326795</v>
+        <v>-3.314262</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.942414</v>
+        <v>-3.895936</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.271587</v>
+        <v>-3.178951</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.156605</v>
+        <v>-4.082127</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.985884</v>
+        <v>-4.940903</v>
       </c>
     </row>
     <row r="28">
@@ -1671,31 +1671,31 @@
         <v>-0.465627</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.7049</v>
+        <v>-3.67979</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.456567</v>
+        <v>-3.427265</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.390427</v>
+        <v>-4.330512</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.71</v>
+        <v>-3.682771</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.320356</v>
+        <v>-3.307823</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.937092</v>
+        <v>-3.890614</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.267453</v>
+        <v>-3.174817</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.151712</v>
+        <v>-4.077234</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.975655</v>
+        <v>-4.930674</v>
       </c>
     </row>
     <row r="30">
@@ -1889,13 +1889,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.128271</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.272881</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000516</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>3.382218</v>
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.128271</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.272881</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000516</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>8.582217999999999</v>
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.00827</v>
+        <v>0.007754</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -5832,16 +5832,16 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.06802900000000001</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08043599999999999</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.091282</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022493</v>
       </c>
       <c r="K124" s="3" t="n">
         <v>0</v>
@@ -5875,16 +5875,16 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.06802900000000001</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08043599999999999</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.091282</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022493</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>0</v>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
@@ -15816,7 +15816,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -16400,7 +16404,11 @@
           <t>Lease payments (Note 7)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -25614,7 +25622,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -25678,7 +25686,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -26824,7 +26832,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -31772,7 +31780,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">

--- a/output/pdf_financials_xlsx/JG.xlsx
+++ b/output/pdf_financials_xlsx/JG.xlsx
@@ -679,25 +679,25 @@
         <v>1.071897</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.173975</v>
+        <v>1.265664</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.191628</v>
+        <v>1.329395</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.146077</v>
+        <v>1.299326</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.107737</v>
+        <v>1.262269</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.190914</v>
+        <v>1.349107</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.351936</v>
+        <v>1.505502</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.393825</v>
+        <v>1.547292</v>
       </c>
     </row>
     <row r="8">
@@ -808,25 +808,25 @@
         <v>1.777167</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.399366</v>
+        <v>1.491055</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.446669</v>
+        <v>1.584436</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.49035</v>
+        <v>1.643599</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.787776</v>
+        <v>1.942308</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.772312</v>
+        <v>1.930505</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.85093</v>
+        <v>2.004496</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.81621</v>
+        <v>1.969677</v>
       </c>
     </row>
     <row r="11">
@@ -17986,7 +17986,11 @@
           <t>Proceeds received from private placement (Note 8)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -24158,7 +24162,11 @@
           <t>Private placement (Note 4(b)(d)) 6,000,000 231,606 68,394</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E238" s="5" t="n">
         <v>0.3</v>
       </c>
@@ -24676,7 +24684,11 @@
           <t>Director fees (Note 7)</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -26382,7 +26394,11 @@
           <t>Director fees (Note 8)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -27486,7 +27502,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
